--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -671,15 +671,29 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>StatEt</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>31-May-26</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -827,15 +841,29 @@
           <t>revenue_pct_gdp</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
+      <c r="B11" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>IMF (tax revenue only, approx.)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15-Jul-26</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -958,12 +986,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -973,7 +1001,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
         </is>
       </c>
     </row>
@@ -1121,15 +1149,29 @@
           <t>eurobonds_outstanding_usd_bn</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jun-26 (defaulted, pre-exchange)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MoFED</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>29-Jun-26</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1211,6 +1253,16 @@
           <t>fitch</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>24-Oct-25</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1218,6 +1270,16 @@
           <t>sp</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20-Dec-23</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1225,11 +1287,44 @@
           <t>moodys</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Caa3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>14-Feb-26</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>IMF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Extended Credit Facility (48-month)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>29-Jul-24</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>In debt distress</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ethiopia.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ethiopia.json</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jun-26 (defaulted, pre-exchange)</t>
+          <t>Jun-26 (defaulted USD 1.0bn 6.625% due 11-Dec-24, XS1151974877; agreement in principle to exchange into USD 880m new 6.15% notes due 15-Jul-29)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MoFED</t>
+          <t>Ministry of Finance (MoFED), Eurobond restructuring agreement in principle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>In debt distress</t>
+          <t>In debt distress (pending restructuring completion)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>StatEt</t>
+          <t>StatEt / NBE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jun-26 (defaulted USD 1.0bn 6.625% due 11-Dec-24, XS1151974877; agreement in principle to exchange into USD 880m new 6.15% notes due 15-Jul-29)</t>
+          <t>Jun-26 (defaulted 6.625% due 11-Dec-24, XS1151974877; nominal before restructuring)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ministry of Finance (MoFED), Eurobond restructuring agreement in principle</t>
+          <t>MoFED Eurobond AIP release</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>In debt distress (pending restructuring completion)</t>
+          <t>in debt distress (pending restructuring completion)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>StatEt / NBE</t>
+          <t>StatEt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jun-26 (defaulted 6.625% due 11-Dec-24, XS1151974877; nominal before restructuring)</t>
+          <t>Jun-26 (defaulted USD 1.0bn 6.625% due 11-Dec-24, XS1151974877, face value)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MoFED Eurobond AIP release</t>
+          <t>MoFED</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20-Dec-23</t>
+          <t>Dec-25</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>in debt distress (pending restructuring completion)</t>
+          <t>in debt distress</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jun-26 (defaulted USD 1.0bn 6.625% due 11-Dec-24, XS1151974877, face value)</t>
+          <t>Oct-26 (defaulted 6.625% 2024 notes, XS1151974877, original face value, pending exchange)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dec-25</t>
+          <t>20-Dec-23</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Credit Facility (48-month)</t>
+          <t>48-month Extended Credit Facility (ECF)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>in debt distress</t>
+          <t>In debt distress (pending restructuring completion)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>StatEt</t>
+          <t>StatEt / NBE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oct-26 (defaulted 6.625% 2024 notes, XS1151974877, original face value, pending exchange)</t>
+          <t>defaulted 6.625% due 11-Dec-24 (XS1151974877), exchange pending</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>48-month Extended Credit Facility (ECF)</t>
+          <t>Extended Credit Facility (48-month)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>In debt distress (pending restructuring completion)</t>
+          <t>in debt distress</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>StatEt / NBE</t>
+          <t>StatEt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>defaulted 6.625% due 11-Dec-24 (XS1151974877), exchange pending</t>
+          <t>Jun-26 (defaulted 6.625% due 11-Dec-24, XS1151974877; agreement in principle to exchange into USD 880m)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Credit Facility (48-month)</t>
+          <t>Extended Credit Facility (48 months)</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ethiopia.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ethiopia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ethiopia.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ethiopia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ethiopia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ethiopia.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ethiopia.json</t>
         </is>
       </c>
     </row>
